--- a/exit_interview_templates/028_exit_interview_checklist--exit_interview_templates.xlsx
+++ b/exit_interview_templates/028_exit_interview_checklist--exit_interview_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'16a',_'value':_1,_'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '16a', 'value': 1, 'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'16b',_'value':_2,_'label':_'career_change'}</t>
+          <t>career_change</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '16b', 'value': 2, 'label': 'Career Change'}</t>
+          <t>Career Change</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'16c',_'value':_3,_'label':_'job_opportunity'}</t>
+          <t>job_opportunity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '16c', 'value': 3, 'label': 'Job Opportunity'}</t>
+          <t>Job Opportunity</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'16d',_'value':_4,_'label':_'health_issues'}</t>
+          <t>health_issues</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '16d', 'value': 4, 'label': 'Health Issues'}</t>
+          <t>Health Issues</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'16e',_'value':_5,_'label':_'family_obligations'}</t>
+          <t>family_obligations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '16e', 'value': 5, 'label': 'Family Obligations'}</t>
+          <t>Family Obligations</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'16f',_'value':_6,_'label':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '16f', 'value': 6, 'label': 'Education'}</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'16g',_'value':_7,_'label':_'company_change'}</t>
+          <t>company_change</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '16g', 'value': 7, 'label': 'Company Change'}</t>
+          <t>Company Change</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'16h',_'value':_8,_'label':_'financial'}</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '16h', 'value': 8, 'label': 'Financial'}</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'16i',_'value':_9,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '16i', 'value': 9, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'16j',_'value':_10,_'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '16j', 'value': 10, 'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'16k',_'value':_11,_'label':_'laid_off'}</t>
+          <t>laid_off</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '16k', 'value': 11, 'label': 'Laid Off'}</t>
+          <t>Laid Off</t>
         </is>
       </c>
     </row>
